--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A0C145-E446-447A-BFD6-E306DBC5937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C2805C-899E-406B-9920-5E26748AACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,15 +772,9 @@
     <t>Small O&amp;M cost to speed up the solver</t>
   </si>
   <si>
-    <t>Heavily weighting "modelling-techical" shutdown costs to avoid too many shutdows of nuclear reactors. The 400 EUR/MW is roughly 60 hours of price difference to VRE.</t>
-  </si>
-  <si>
     <t>nuclearFlexible</t>
   </si>
   <si>
-    <t>A nuclear unit with much lower ramp costs for France and flexible part of OL3</t>
-  </si>
-  <si>
     <t>Assuming 20 EUR/MWh cost (grid fees, taxes, …) for input electricity</t>
   </si>
   <si>
@@ -806,6 +800,12 @@
   </si>
   <si>
     <t>Assuming 3% losses in cell and 3% in inverter both directions for all BESS</t>
+  </si>
+  <si>
+    <t>Heavily weighting "modelling-techical" shutdown costs to avoid too many shutdows of nuclear reactors. The 300 EUR/MW is roughly (300 / (3-1.5)) = 200 hours of price difference to VRE.</t>
+  </si>
+  <si>
+    <t>A nuclear unit with much lower ramp costs for flexible part of countrys operation</t>
   </si>
 </sst>
 </file>
@@ -1503,14 +1503,14 @@
         <v>1</v>
       </c>
       <c r="S7" s="1">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="T7" s="19"/>
       <c r="Y7" s="1">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Z7" s="1">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AC7" s="1" t="s">
         <v>232</v>
@@ -1552,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1617,14 +1617,14 @@
         <v>1</v>
       </c>
       <c r="S10" s="1">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T10" s="19"/>
       <c r="Y10" s="1">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z10" s="1">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1653,14 +1653,14 @@
         <v>1</v>
       </c>
       <c r="S11" s="1">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="T11" s="19"/>
       <c r="Y11" s="1">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Z11" s="1">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1809,7 +1809,7 @@
         <v>0.36</v>
       </c>
       <c r="P15" s="1">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="Q15" s="1">
         <v>0.5</v>
@@ -1909,7 +1909,7 @@
         <v>0.37</v>
       </c>
       <c r="P17" s="1">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="Q17" s="1">
         <v>0.5</v>
@@ -2009,7 +2009,7 @@
         <v>0.31999999999999995</v>
       </c>
       <c r="P19" s="1">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="Q19" s="1">
         <v>0.5</v>
@@ -2462,7 +2462,7 @@
         <v>0.37</v>
       </c>
       <c r="P28" s="1">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="Q28" s="1">
         <v>0.4</v>
@@ -2615,7 +2615,7 @@
         <v>0.43000000000000005</v>
       </c>
       <c r="P31" s="1">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="Q31" s="1">
         <v>0.25</v>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="S48" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" s="23"/>
       <c r="U48" s="1">
@@ -3468,13 +3468,13 @@
         <v>0.05</v>
       </c>
       <c r="Y48" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Z48" s="13">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="AC48" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3485,10 +3485,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>5</v>
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="13">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="T49" s="23"/>
       <c r="U49" s="1">
@@ -3525,7 +3525,7 @@
         <v>45</v>
       </c>
       <c r="AC49" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>4</v>
       </c>
       <c r="AC55" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4007,7 +4007,7 @@
         <v>20</v>
       </c>
       <c r="AC61" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4249,7 +4249,7 @@
         <v>20</v>
       </c>
       <c r="AC66" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>100</v>
       </c>
       <c r="AC79" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5270,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="AC90" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5281,10 +5281,10 @@
         <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>59</v>
@@ -5309,7 +5309,7 @@
         <v>25</v>
       </c>
       <c r="AC91" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="92" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">

--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C2805C-899E-406B-9920-5E26748AACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C3986A-803F-47C5-BDE9-B4DC97B3B64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="unittypedata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unittypedata!$C$1:$AB$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unittypedata!$C$1:$AA$58</definedName>
     <definedName name="Bottom">OFFSET(#REF!,1,0,COUNT(#REF!),1)</definedName>
     <definedName name="fd">OFFSET(#REF!,1,0,COUNT(#REF!),1)</definedName>
     <definedName name="Labels">OFFSET(Bottom,0,-1)</definedName>
@@ -68,23 +68,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="245">
   <si>
     <t>vomCosts</t>
   </si>
   <si>
-    <t>maxRampUp</t>
-  </si>
-  <si>
-    <t>maxRampDown</t>
-  </si>
-  <si>
     <t>cb</t>
   </si>
   <si>
-    <t>useTimeseriesAvailability</t>
-  </si>
-  <si>
     <t>Nuclear</t>
   </si>
   <si>
@@ -670,9 +661,6 @@
     <t>op01</t>
   </si>
   <si>
-    <t>rampUpCost</t>
-  </si>
-  <si>
     <t>vomCosts_input1</t>
   </si>
   <si>
@@ -733,9 +721,6 @@
     <t>CHPgasExtraction</t>
   </si>
   <si>
-    <t>rampDownCost</t>
-  </si>
-  <si>
     <t># VRE</t>
   </si>
   <si>
@@ -769,9 +754,6 @@
     <t>Hydro O&amp;M costs approximated from https://link.springer.com/article/10.1007/s12667-023-00589-w</t>
   </si>
   <si>
-    <t>Small O&amp;M cost to speed up the solver</t>
-  </si>
-  <si>
     <t>nuclearFlexible</t>
   </si>
   <si>
@@ -799,13 +781,28 @@
     <t>Nuclear-flex</t>
   </si>
   <si>
-    <t>Assuming 3% losses in cell and 3% in inverter both directions for all BESS</t>
-  </si>
-  <si>
     <t>Heavily weighting "modelling-techical" shutdown costs to avoid too many shutdows of nuclear reactors. The 300 EUR/MW is roughly (300 / (3-1.5)) = 200 hours of price difference to VRE.</t>
   </si>
   <si>
     <t>A nuclear unit with much lower ramp costs for flexible part of countrys operation</t>
+  </si>
+  <si>
+    <t>disabled-rampUpCost</t>
+  </si>
+  <si>
+    <t>disabled-rampDownCost</t>
+  </si>
+  <si>
+    <t>disabled-maxRampUp</t>
+  </si>
+  <si>
+    <t>disabled-maxRampDown</t>
+  </si>
+  <si>
+    <t>Assuming 3% losses in cell and 3% in inverter both directions (charge+discharge) for all BESS</t>
+  </si>
+  <si>
+    <t>No O&amp;M cost to enable better automatic scaling</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AB96"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -1215,103 +1212,99 @@
     <col min="21" max="22" width="8.42578125" customWidth="1"/>
     <col min="25" max="26" width="14" customWidth="1"/>
     <col min="27" max="27" width="15.85546875" customWidth="1"/>
-    <col min="28" max="28" width="10.140625" customWidth="1"/>
-    <col min="29" max="29" width="78.140625" bestFit="1" customWidth="1"/>
-    <col min="1025" max="1025" width="9.140625" customWidth="1"/>
+    <col min="28" max="28" width="78.140625" bestFit="1" customWidth="1"/>
+    <col min="1024" max="1024" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="L1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="P1" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="15"/>
@@ -1340,98 +1333,91 @@
       <c r="Z2" s="15"/>
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-    </row>
-    <row r="3" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="19">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="T3" s="19"/>
+      <c r="AB3" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="19">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="19"/>
+    </row>
+    <row r="5" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="19">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>1</v>
-      </c>
-      <c r="S3" s="1">
-        <v>1</v>
-      </c>
-      <c r="T3" s="19"/>
-      <c r="AC3" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="19">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="T4" s="19"/>
-    </row>
-    <row r="5" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="19">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
@@ -1439,14 +1425,11 @@
       <c r="Q5" s="1">
         <v>1</v>
       </c>
-      <c r="S5" s="1">
-        <v>0.5</v>
-      </c>
       <c r="T5" s="19"/>
     </row>
-    <row r="6" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="15"/>
@@ -1475,35 +1458,34 @@
       <c r="Z6" s="15"/>
       <c r="AA6" s="15"/>
       <c r="AB6" s="15"/>
-      <c r="AC6" s="15"/>
-    </row>
-    <row r="7" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B7" s="19">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="Q7" s="1">
         <v>1</v>
       </c>
       <c r="S7" s="1">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="T7" s="19"/>
       <c r="Y7" s="1">
@@ -1512,37 +1494,37 @@
       <c r="Z7" s="1">
         <v>5.5</v>
       </c>
-      <c r="AC7" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB7" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O8" s="1">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="Q8" s="1">
         <v>1</v>
       </c>
       <c r="S8" s="1">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="T8" s="19"/>
       <c r="Y8" s="1">
@@ -1551,37 +1533,37 @@
       <c r="Z8" s="1">
         <v>5</v>
       </c>
-      <c r="AC8" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB8" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O9" s="1">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="Q9" s="1">
         <v>1</v>
       </c>
       <c r="S9" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T9" s="19"/>
       <c r="Y9" s="1">
@@ -1591,24 +1573,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" s="19">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O10" s="1">
         <v>0.8</v>
@@ -1617,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="1">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="T10" s="19"/>
       <c r="Y10" s="1">
@@ -1627,33 +1609,33 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B11" s="19">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O11" s="1">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
       </c>
       <c r="S11" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="T11" s="19"/>
       <c r="Y11" s="1">
@@ -1663,24 +1645,24 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B12" s="19">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O12" s="1">
         <v>0.8</v>
@@ -1689,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="S12" s="1">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T12" s="19"/>
       <c r="Y12" s="1">
@@ -1699,9 +1681,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="15"/>
@@ -1730,29 +1712,28 @@
       <c r="Z13" s="15"/>
       <c r="AA13" s="15"/>
       <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-    </row>
-    <row r="14" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O14" s="1">
         <v>0.26</v>
@@ -1783,27 +1764,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B15" s="19">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O15" s="1">
         <v>0.36</v>
@@ -1834,27 +1815,27 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O16" s="1">
         <v>0.36</v>
@@ -1887,23 +1868,23 @@
     </row>
     <row r="17" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O17" s="1">
         <v>0.37</v>
@@ -1936,25 +1917,25 @@
     </row>
     <row r="18" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B18" s="19">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O18" s="1">
         <v>0.37</v>
@@ -1987,23 +1968,23 @@
     </row>
     <row r="19" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" s="19">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O19" s="1">
         <v>0.31999999999999995</v>
@@ -2036,25 +2017,25 @@
     </row>
     <row r="20" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B20" s="19">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O20" s="1">
         <v>0.31999999999999995</v>
@@ -2087,25 +2068,25 @@
     </row>
     <row r="21" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B21" s="19">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O21" s="1">
         <v>0.43000000000000005</v>
@@ -2138,22 +2119,22 @@
     </row>
     <row r="22" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B22" s="19">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O22" s="1">
         <v>0.35</v>
@@ -2186,25 +2167,25 @@
     </row>
     <row r="23" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B23" s="19">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O23" s="1">
         <v>0.31999999999999995</v>
@@ -2219,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="T23" s="19"/>
       <c r="U23" s="1">
@@ -2237,25 +2218,25 @@
     </row>
     <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B24" s="19">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O24" s="1">
         <v>0.37</v>
@@ -2288,25 +2269,25 @@
     </row>
     <row r="25" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B25" s="19">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O25" s="1">
         <v>0.31999999999999995</v>
@@ -2339,22 +2320,22 @@
     </row>
     <row r="26" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B26" s="19">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O26" s="1">
         <v>0.28000000000000003</v>
@@ -2387,25 +2368,25 @@
     </row>
     <row r="27" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B27" s="19">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O27" s="1">
         <v>0.31999999999999995</v>
@@ -2438,25 +2419,25 @@
     </row>
     <row r="28" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B28" s="19">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O28" s="1">
         <v>0.37</v>
@@ -2489,25 +2470,25 @@
     </row>
     <row r="29" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B29" s="19">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O29" s="1">
         <v>0.37</v>
@@ -2540,25 +2521,25 @@
     </row>
     <row r="30" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B30" s="19">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O30" s="1">
         <v>0.31999999999999995</v>
@@ -2591,25 +2572,25 @@
     </row>
     <row r="31" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B31" s="19">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O31" s="1">
         <v>0.43000000000000005</v>
@@ -2642,25 +2623,25 @@
     </row>
     <row r="32" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B32" s="19">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O32" s="1">
         <v>0.43000000000000005</v>
@@ -2691,24 +2672,24 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" s="19">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B33" s="19">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O33" s="1">
         <v>0.27</v>
@@ -2723,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="T33" s="19"/>
       <c r="U33" s="1">
@@ -2739,27 +2720,27 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B34" s="19">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O34" s="1">
         <v>0.38</v>
@@ -2774,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="T34" s="19"/>
       <c r="U34" s="1">
@@ -2790,27 +2771,27 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B35" s="19">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O35" s="1">
         <v>0.32999999999999996</v>
@@ -2825,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="1">
-        <v>1.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="T35" s="19"/>
       <c r="U35" s="1">
@@ -2841,27 +2822,27 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B36" s="19">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O36" s="1">
         <v>0.31999999999999995</v>
@@ -2876,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T36" s="19"/>
       <c r="U36" s="1">
@@ -2892,27 +2873,27 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B37" s="19">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O37" s="1">
         <v>0.39</v>
@@ -2927,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T37" s="19"/>
       <c r="U37" s="1">
@@ -2943,27 +2924,27 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B38" s="19">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O38" s="1">
         <v>0.54999999999999993</v>
@@ -2978,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="S38" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T38" s="19"/>
       <c r="U38" s="1">
@@ -2994,27 +2975,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B39" s="19">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O39" s="1">
         <v>0.53</v>
@@ -3029,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="S39" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T39" s="19"/>
       <c r="U39" s="1">
@@ -3045,24 +3026,24 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B40" s="19">
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O40" s="1">
         <v>0.29000000000000004</v>
@@ -3077,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="S40" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T40" s="19"/>
       <c r="U40" s="1">
@@ -3093,27 +3074,27 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B41" s="19">
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O41" s="1">
         <v>0.44999999999999996</v>
@@ -3128,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="S41" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T41" s="19"/>
       <c r="U41" s="1">
@@ -3144,27 +3125,27 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B42" s="19">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O42" s="1">
         <v>0.37</v>
@@ -3179,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="S42" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T42" s="19"/>
       <c r="U42" s="1">
@@ -3195,27 +3176,27 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="43" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B43" s="19">
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O43" s="1">
         <v>0.56999999999999995</v>
@@ -3230,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="S43" s="1">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="T43" s="19"/>
       <c r="U43" s="1">
@@ -3246,9 +3227,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="9"/>
@@ -3277,32 +3258,31 @@
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
       <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-    </row>
-    <row r="45" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B45" s="19">
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M45" s="1">
         <v>0</v>
@@ -3336,30 +3316,30 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B46" s="19">
         <v>1</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M46" s="1">
         <v>0</v>
@@ -3393,9 +3373,9 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="9"/>
@@ -3424,26 +3404,25 @@
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
       <c r="AB47" s="9"/>
-      <c r="AC47" s="9"/>
-    </row>
-    <row r="48" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B48" s="19">
         <v>1</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O48" s="13">
         <v>0.33</v>
@@ -3473,28 +3452,28 @@
       <c r="Z48" s="13">
         <v>240</v>
       </c>
-      <c r="AC48" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB48" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B49" s="19">
         <v>1</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O49" s="13">
         <v>0.33</v>
@@ -3524,13 +3503,13 @@
       <c r="Z49" s="13">
         <v>45</v>
       </c>
-      <c r="AC49" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB49" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15"/>
@@ -3559,29 +3538,28 @@
       <c r="Z50" s="15"/>
       <c r="AA50" s="15"/>
       <c r="AB50" s="15"/>
-      <c r="AC50" s="15"/>
-    </row>
-    <row r="51" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B51" s="19">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O51" s="1">
         <v>0.9</v>
@@ -3618,30 +3596,30 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B52" s="19">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O52" s="1">
         <v>0.9</v>
@@ -3678,30 +3656,30 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B53" s="19">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O53" s="1">
         <v>0.9</v>
@@ -3738,9 +3716,9 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="54" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15"/>
@@ -3769,26 +3747,25 @@
       <c r="Z54" s="15"/>
       <c r="AA54" s="15"/>
       <c r="AB54" s="15"/>
-      <c r="AC54" s="15"/>
-    </row>
-    <row r="55" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B55" s="19">
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O55" s="1">
         <v>0.94</v>
@@ -3797,34 +3774,34 @@
         <v>1</v>
       </c>
       <c r="S55" s="1">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="T55" s="19"/>
       <c r="AA55" s="1">
         <v>4</v>
       </c>
-      <c r="AC55" s="1" t="s">
+      <c r="AB55" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B56" s="19">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O56" s="1">
         <v>0.94</v>
@@ -3833,31 +3810,31 @@
         <v>1</v>
       </c>
       <c r="S56" s="1">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T56" s="19"/>
       <c r="AA56" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B57" s="19">
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="O57" s="1">
         <v>0.94</v>
@@ -3866,28 +3843,28 @@
         <v>1</v>
       </c>
       <c r="S57" s="1">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="T57" s="19"/>
     </row>
-    <row r="58" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="O58" s="1">
         <v>0.94</v>
@@ -3896,13 +3873,13 @@
         <v>1</v>
       </c>
       <c r="S58" s="1">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T58" s="19"/>
     </row>
-    <row r="59" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15"/>
@@ -3931,29 +3908,28 @@
       <c r="Z59" s="15"/>
       <c r="AA59" s="15"/>
       <c r="AB59" s="15"/>
-      <c r="AC59" s="15"/>
-    </row>
-    <row r="60" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B60" s="19">
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O60" s="1">
         <v>1</v>
@@ -3969,24 +3945,24 @@
       </c>
       <c r="T60" s="19"/>
     </row>
-    <row r="61" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B61" s="19">
         <v>1</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O61" s="1">
         <v>2.8</v>
@@ -4006,31 +3982,31 @@
       <c r="T61" s="19">
         <v>20</v>
       </c>
-      <c r="AC61" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB61" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B62" s="19">
         <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O62" s="1">
         <v>0.9</v>
@@ -4061,27 +4037,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B63" s="19">
         <v>1</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O63" s="1">
         <v>0.9</v>
@@ -4112,27 +4088,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B64" s="19">
         <v>1</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O64" s="1">
         <v>0.9</v>
@@ -4163,24 +4139,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B65" s="19">
         <v>1</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O65" s="1">
         <v>0.9</v>
@@ -4211,24 +4187,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B66" s="19">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O66" s="1">
         <v>0.98</v>
@@ -4248,34 +4224,34 @@
       <c r="T66" s="19">
         <v>20</v>
       </c>
-      <c r="AC66" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB66" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B67" s="19">
         <v>1</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O67" s="1">
         <v>0.89</v>
@@ -4309,30 +4285,30 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B68" s="19">
         <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O68" s="1">
         <v>0.89</v>
@@ -4366,27 +4342,27 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B69" s="19">
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O69" s="1">
         <v>0.89</v>
@@ -4420,30 +4396,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B70" s="19">
         <v>1</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O70" s="1">
         <v>0.9</v>
@@ -4477,27 +4453,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B71" s="19">
         <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O71" s="1">
         <v>0.9</v>
@@ -4522,30 +4498,30 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="72" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B72" s="19">
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O72" s="1">
         <v>0.89</v>
@@ -4582,27 +4558,27 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B73" s="19">
         <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O73" s="1">
         <v>0.89</v>
@@ -4639,30 +4615,30 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B74" s="19">
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O74" s="1">
         <v>0.9</v>
@@ -4699,30 +4675,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B75" s="19">
         <v>1</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="J75" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O75" s="1">
         <v>0.55000000000000004</v>
@@ -4756,30 +4732,30 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="76" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B76" s="19">
         <v>1</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O76" s="1">
         <v>0.9</v>
@@ -4813,24 +4789,24 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="77" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B77" s="19">
         <v>1</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O77" s="1">
         <v>0.99</v>
@@ -4839,31 +4815,31 @@
         <v>1</v>
       </c>
       <c r="S77" s="1">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T77" s="19"/>
       <c r="AA77" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B78" s="19">
         <v>1</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O78" s="1">
         <v>0.99</v>
@@ -4872,28 +4848,28 @@
         <v>1</v>
       </c>
       <c r="S78" s="1">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="T78" s="19"/>
     </row>
-    <row r="79" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B79" s="19">
         <v>1</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="K79" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O79" s="1">
         <v>0.99</v>
@@ -4902,34 +4878,34 @@
         <v>1</v>
       </c>
       <c r="S79" s="1">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T79" s="19"/>
       <c r="AA79" s="1">
         <v>100</v>
       </c>
-      <c r="AC79" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB79" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B80" s="19">
         <v>1</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O80" s="1">
         <v>0.99</v>
@@ -4938,28 +4914,28 @@
         <v>1</v>
       </c>
       <c r="S80" s="1">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T80" s="19"/>
     </row>
-    <row r="81" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B81" s="19">
         <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O81" s="1">
         <v>0.99</v>
@@ -4975,24 +4951,24 @@
         <v>450</v>
       </c>
     </row>
-    <row r="82" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B82" s="19">
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="O82" s="1">
         <v>0.99</v>
@@ -5005,9 +4981,9 @@
       </c>
       <c r="T82" s="19"/>
     </row>
-    <row r="83" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="15"/>
@@ -5036,29 +5012,28 @@
       <c r="Z83" s="15"/>
       <c r="AA83" s="15"/>
       <c r="AB83" s="15"/>
-      <c r="AC83" s="15"/>
-    </row>
-    <row r="84" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B84" s="19">
         <v>1</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F84" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O84" s="1">
         <v>1</v>
@@ -5070,27 +5045,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B85" s="19">
         <v>1</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F85" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O85" s="1">
         <v>1</v>
@@ -5102,27 +5077,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B86" s="19">
         <v>1</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E86" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O86" s="1">
         <v>1</v>
@@ -5135,27 +5110,27 @@
       </c>
       <c r="T86" s="19"/>
     </row>
-    <row r="87" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B87" s="19">
         <v>1</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E87" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O87" s="1">
         <v>1</v>
@@ -5168,27 +5143,27 @@
       </c>
       <c r="T87" s="19"/>
     </row>
-    <row r="88" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B88" s="19">
         <v>1</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E88" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O88" s="1">
         <v>1</v>
@@ -5201,9 +5176,9 @@
       </c>
       <c r="T88" s="19"/>
     </row>
-    <row r="89" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="15"/>
@@ -5232,26 +5207,25 @@
       <c r="Z89" s="15"/>
       <c r="AA89" s="15"/>
       <c r="AB89" s="15"/>
-      <c r="AC89" s="15"/>
-    </row>
-    <row r="90" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B90" s="19">
         <v>1</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O90" s="1">
         <v>0.61</v>
@@ -5260,7 +5234,7 @@
         <v>1</v>
       </c>
       <c r="S90" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T90" s="19"/>
       <c r="Y90" s="1">
@@ -5269,28 +5243,28 @@
       <c r="Z90" s="1">
         <v>15</v>
       </c>
-      <c r="AC90" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB90" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B91" s="19">
         <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O91" s="1">
         <v>0.8</v>
@@ -5299,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="S91" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T91" s="19"/>
       <c r="Y91" s="1">
@@ -5308,28 +5282,28 @@
       <c r="Z91" s="1">
         <v>25</v>
       </c>
-      <c r="AC91" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB91" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B92" s="19">
         <v>1</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O92" s="1">
         <f>P92-0.03</f>
@@ -5352,24 +5326,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B93" s="19">
         <v>1</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O93" s="1">
         <v>1</v>
@@ -5384,31 +5358,31 @@
         <v>1</v>
       </c>
       <c r="S93" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T93" s="19"/>
       <c r="AA93" s="16">
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B94" s="19">
         <v>1</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="O94" s="1">
         <v>0.99</v>
@@ -5423,29 +5397,29 @@
         <v>1</v>
       </c>
       <c r="S94" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T94" s="19"/>
       <c r="AA94" s="16"/>
     </row>
-    <row r="95" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B95" s="19">
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="K95" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O95" s="1">
         <v>1</v>
@@ -5460,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="S95" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T95" s="19"/>
       <c r="Y95" s="1">
@@ -5470,24 +5444,24 @@
         <v>924</v>
       </c>
     </row>
-    <row r="96" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B96" s="19">
         <v>1</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O96" s="1">
         <v>0.99</v>
@@ -5502,7 +5476,7 @@
         <v>1</v>
       </c>
       <c r="S96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T96" s="19"/>
       <c r="Y96" s="1">
@@ -5511,8 +5485,8 @@
       <c r="AA96" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:AB43" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AB43">
+  <autoFilter ref="C1:AA43" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:AA43">
       <sortCondition descending="1" ref="D1:D43"/>
     </sortState>
   </autoFilter>

--- a/src_files/data_files/unittypedata_compilation.xlsx
+++ b/src_files/data_files/unittypedata_compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C3986A-803F-47C5-BDE9-B4DC97B3B64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8E5763-CDA7-4C2F-AF2E-6CE5A5EA4289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,121 +688,121 @@
     <t>oilshaleCHP</t>
   </si>
   <si>
+    <t>Generator_ID</t>
+  </si>
+  <si>
+    <t>ETS-CO2</t>
+  </si>
+  <si>
+    <t>Coal HOB</t>
+  </si>
+  <si>
+    <t>HOBcoal</t>
+  </si>
+  <si>
+    <t>Coal CHP extraction</t>
+  </si>
+  <si>
+    <t>CHPcoalExtraction</t>
+  </si>
+  <si>
+    <t>Bio CHP extraction</t>
+  </si>
+  <si>
+    <t>CHPbioExtraction</t>
+  </si>
+  <si>
+    <t>Gas CHP extraction</t>
+  </si>
+  <si>
+    <t>CHPgasExtraction</t>
+  </si>
+  <si>
+    <t>Hydro O&amp;M costs approximated from https://link.springer.com/article/10.1007/s12667-023-00589-w</t>
+  </si>
+  <si>
+    <t>nuclearFlexible</t>
+  </si>
+  <si>
+    <t>Assuming 20 EUR/MWh cost (grid fees, taxes, …) for input electricity</t>
+  </si>
+  <si>
+    <t>Electrolyser-SOEC</t>
+  </si>
+  <si>
+    <t>ElectrolyserSOEC</t>
+  </si>
+  <si>
+    <t>Alkaline/PEM efficiency from LHV. Start up costs are an own estimate of heating up the device (10-20 mins) and wear and tear (10 h lost lifetime).</t>
+  </si>
+  <si>
+    <t>SOEC efficiency from LHV.  Start up costs are an own estimate of heating up the device (10-20 mins) and wear and tear (10 h lost lifetime).</t>
+  </si>
+  <si>
+    <t>Differentiating heat storage types by vomcost to aid solver</t>
+  </si>
+  <si>
+    <t>Differentiating hydro types by vomcost and rampcost to help solver.</t>
+  </si>
+  <si>
+    <t>Nuclear-flex</t>
+  </si>
+  <si>
+    <t>Heavily weighting "modelling-techical" shutdown costs to avoid too many shutdows of nuclear reactors. The 300 EUR/MW is roughly (300 / (3-1.5)) = 200 hours of price difference to VRE.</t>
+  </si>
+  <si>
+    <t>A nuclear unit with much lower ramp costs for flexible part of countrys operation</t>
+  </si>
+  <si>
+    <t>disabled-rampUpCost</t>
+  </si>
+  <si>
+    <t>disabled-rampDownCost</t>
+  </si>
+  <si>
+    <t>disabled-maxRampUp</t>
+  </si>
+  <si>
+    <t>disabled-maxRampDown</t>
+  </si>
+  <si>
+    <t>Assuming 3% losses in cell and 3% in inverter both directions (charge+discharge) for all BESS</t>
+  </si>
+  <si>
+    <t>No O&amp;M cost to enable better automatic scaling</t>
+  </si>
+  <si>
+    <t>## VRE</t>
+  </si>
+  <si>
+    <t>## Hydro</t>
+  </si>
+  <si>
+    <t>## Thermal condensing power</t>
+  </si>
+  <si>
+    <t>## CCS</t>
+  </si>
+  <si>
+    <t>## Nuclear</t>
+  </si>
+  <si>
+    <t>## Industry</t>
+  </si>
+  <si>
+    <t>## Electricity storages</t>
+  </si>
+  <si>
+    <t>## District heating</t>
+  </si>
+  <si>
+    <t>## Demand response</t>
+  </si>
+  <si>
+    <t>## Hydrogen</t>
+  </si>
+  <si>
     <t>Note</t>
-  </si>
-  <si>
-    <t>Generator_ID</t>
-  </si>
-  <si>
-    <t>ETS-CO2</t>
-  </si>
-  <si>
-    <t>Coal HOB</t>
-  </si>
-  <si>
-    <t>HOBcoal</t>
-  </si>
-  <si>
-    <t>Coal CHP extraction</t>
-  </si>
-  <si>
-    <t>CHPcoalExtraction</t>
-  </si>
-  <si>
-    <t>Bio CHP extraction</t>
-  </si>
-  <si>
-    <t>CHPbioExtraction</t>
-  </si>
-  <si>
-    <t>Gas CHP extraction</t>
-  </si>
-  <si>
-    <t>CHPgasExtraction</t>
-  </si>
-  <si>
-    <t># VRE</t>
-  </si>
-  <si>
-    <t># Hydro</t>
-  </si>
-  <si>
-    <t># Nuclear</t>
-  </si>
-  <si>
-    <t># Hydrogen</t>
-  </si>
-  <si>
-    <t># Demand response</t>
-  </si>
-  <si>
-    <t># District heating</t>
-  </si>
-  <si>
-    <t># Thermal condensing power</t>
-  </si>
-  <si>
-    <t># CCS</t>
-  </si>
-  <si>
-    <t># Industry</t>
-  </si>
-  <si>
-    <t># Electricity storages</t>
-  </si>
-  <si>
-    <t>Hydro O&amp;M costs approximated from https://link.springer.com/article/10.1007/s12667-023-00589-w</t>
-  </si>
-  <si>
-    <t>nuclearFlexible</t>
-  </si>
-  <si>
-    <t>Assuming 20 EUR/MWh cost (grid fees, taxes, …) for input electricity</t>
-  </si>
-  <si>
-    <t>Electrolyser-SOEC</t>
-  </si>
-  <si>
-    <t>ElectrolyserSOEC</t>
-  </si>
-  <si>
-    <t>Alkaline/PEM efficiency from LHV. Start up costs are an own estimate of heating up the device (10-20 mins) and wear and tear (10 h lost lifetime).</t>
-  </si>
-  <si>
-    <t>SOEC efficiency from LHV.  Start up costs are an own estimate of heating up the device (10-20 mins) and wear and tear (10 h lost lifetime).</t>
-  </si>
-  <si>
-    <t>Differentiating heat storage types by vomcost to aid solver</t>
-  </si>
-  <si>
-    <t>Differentiating hydro types by vomcost and rampcost to help solver.</t>
-  </si>
-  <si>
-    <t>Nuclear-flex</t>
-  </si>
-  <si>
-    <t>Heavily weighting "modelling-techical" shutdown costs to avoid too many shutdows of nuclear reactors. The 300 EUR/MW is roughly (300 / (3-1.5)) = 200 hours of price difference to VRE.</t>
-  </si>
-  <si>
-    <t>A nuclear unit with much lower ramp costs for flexible part of countrys operation</t>
-  </si>
-  <si>
-    <t>disabled-rampUpCost</t>
-  </si>
-  <si>
-    <t>disabled-rampDownCost</t>
-  </si>
-  <si>
-    <t>disabled-maxRampUp</t>
-  </si>
-  <si>
-    <t>disabled-maxRampDown</t>
-  </si>
-  <si>
-    <t>Assuming 3% losses in cell and 3% in inverter both directions (charge+discharge) for all BESS</t>
-  </si>
-  <si>
-    <t>No O&amp;M cost to enable better automatic scaling</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1224,7 @@
         <v>102</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>190</v>
@@ -1278,10 +1278,10 @@
         <v>197</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>1</v>
@@ -1290,21 +1290,21 @@
         <v>100</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="AA1" s="3" t="s">
         <v>183</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="15"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T3" s="19"/>
       <c r="AB3" s="1" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="6" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="15"/>
@@ -1495,7 +1495,7 @@
         <v>5.5</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1534,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="13" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="15"/>
@@ -1727,7 +1727,7 @@
         <v>139</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>34</v>
@@ -1778,7 +1778,7 @@
         <v>141</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>41</v>
@@ -1829,7 +1829,7 @@
         <v>140</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>34</v>
@@ -1929,7 +1929,7 @@
         <v>112</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>12</v>
@@ -2029,7 +2029,7 @@
         <v>111</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>12</v>
@@ -2080,7 +2080,7 @@
         <v>113</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>12</v>
@@ -2179,7 +2179,7 @@
         <v>136</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>30</v>
@@ -2230,7 +2230,7 @@
         <v>138</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>31</v>
@@ -2281,7 +2281,7 @@
         <v>137</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>31</v>
@@ -2380,7 +2380,7 @@
         <v>120</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>41</v>
@@ -2431,7 +2431,7 @@
         <v>121</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>41</v>
@@ -2482,7 +2482,7 @@
         <v>117</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>4</v>
@@ -2533,7 +2533,7 @@
         <v>116</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>4</v>
@@ -2584,7 +2584,7 @@
         <v>119</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>41</v>
@@ -2635,7 +2635,7 @@
         <v>118</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>4</v>
@@ -2734,7 +2734,7 @@
         <v>124</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>19</v>
@@ -2785,7 +2785,7 @@
         <v>123</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>19</v>
@@ -2836,7 +2836,7 @@
         <v>131</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>19</v>
@@ -2887,7 +2887,7 @@
         <v>132</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>19</v>
@@ -2938,7 +2938,7 @@
         <v>128</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>19</v>
@@ -2989,7 +2989,7 @@
         <v>127</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>19</v>
@@ -3088,7 +3088,7 @@
         <v>126</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>19</v>
@@ -3139,7 +3139,7 @@
         <v>125</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>19</v>
@@ -3190,7 +3190,7 @@
         <v>129</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>19</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="9"/>
@@ -3273,7 +3273,7 @@
         <v>178</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>4</v>
@@ -3330,7 +3330,7 @@
         <v>130</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>19</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="9"/>
@@ -3453,7 +3453,7 @@
         <v>240</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3464,10 +3464,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>2</v>
@@ -3504,12 +3504,12 @@
         <v>45</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="15"/>
@@ -3610,7 +3610,7 @@
         <v>201</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>4</v>
@@ -3670,7 +3670,7 @@
         <v>203</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>19</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="54" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="15"/>
@@ -3781,7 +3781,7 @@
         <v>4</v>
       </c>
       <c r="AB55" s="1" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3879,7 +3879,7 @@
     </row>
     <row r="59" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="15"/>
@@ -3983,7 +3983,7 @@
         <v>20</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>144</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>45</v>
@@ -4051,7 +4051,7 @@
         <v>142</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>31</v>
@@ -4102,7 +4102,7 @@
         <v>135</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>19</v>
@@ -4225,7 +4225,7 @@
         <v>20</v>
       </c>
       <c r="AB66" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4242,7 +4242,7 @@
         <v>143</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>45</v>
@@ -4299,7 +4299,7 @@
         <v>122</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>4</v>
@@ -4410,7 +4410,7 @@
         <v>133</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>19</v>
@@ -4461,13 +4461,13 @@
         <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="I71" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>4</v>
@@ -4506,13 +4506,13 @@
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="I72" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>4</v>
@@ -4566,10 +4566,10 @@
         <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>41</v>
@@ -4623,13 +4623,13 @@
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="I74" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>19</v>
@@ -4689,7 +4689,7 @@
         <v>205</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>34</v>
@@ -4746,7 +4746,7 @@
         <v>134</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>19</v>
@@ -4885,7 +4885,7 @@
         <v>100</v>
       </c>
       <c r="AB79" s="1" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="83" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="15"/>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="15"/>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="AB90" s="1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5255,10 +5255,10 @@
         <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>56</v>
@@ -5283,7 +5283,7 @@
         <v>25</v>
       </c>
       <c r="AB91" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
